--- a/report.xlsx
+++ b/report.xlsx
@@ -540,14 +540,14 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมขนาดใหญ่ที่ค่อนข้างไร้ชีวิตชีวา แผนกต้อนรับเย็นชาในล็อบบี้ที่ดูเย็นชา (และไม่น่าสนใจ) ห้องพักกว้างขวางมาก มีระเบียงมองเห็นสระว่ายน้ำและวิวแม่น้ำในระยะไกล สะดวกสบาย ห้องน้ำขนาดใหญ่และมีอุปกรณ์ครบ</t>
+          <t>หอพักสะอาดกว้างขวาง บรรยากาศดีวิวติดแม่น้ำกก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,16 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานดูแลดีมาก โดยเฉพาะในส่วนห้องอาหารน้องๆน่ารักมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -602,80 +606,92 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอับอากาศไม่ถ่ายเท   น้ำอุ่นไม่ดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>เคยไปใช้บริการสระว่ายน้ำ​ โอเคเลยครับ บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ดีมากค่ะะ สระว่ายน้ำใหญ่สนุกมากกก✌🏻🤟🏻 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -689,27 +705,31 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาดเงียบดีนอนหลับสะบายคะ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -718,22 +738,26 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ลิฟต์เสียตลอดเวลา มาใช้งานเสียความรู้สึก ประเภทการเดินทาง ธุรกิจ ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1 ความปลอดภัย ไม่ดี</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -747,22 +771,26 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>โดยรวมแล้ว ดีเลย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ดี สะอาด เรียบร้อย ความสามารถเดินได้ ทั่วไป ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -776,12 +804,16 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ต้นไม้เยอะ ยุงเลยชุม ตอนกลางคืนได้ยินเสียงหนูแทะไม้ทั้งคืน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -805,12 +837,16 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด สดวกในการเดินทาง ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -834,12 +870,16 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมนรา มีสระว่ายน้ำ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -865,7 +905,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-06-24 04:16) มีรีวิวใหม่ 1 รายการ | เทียบรอบก่อน 2026-06-24 02:08</t>
+          <t>รอบนี้ (2026-06-25 02:50) มีรีวิวใหม่ 151 รายการ | เทียบรอบก่อน 2026-06-24 04:16</t>
         </is>
       </c>
     </row>
@@ -899,23 +939,3473 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Forte-armando</t>
+          <t>muk muk</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมขนาดใหญ่ที่ค่อนข้างไร้ชีวิตชีวา แผนกต้อนรับเย็นชาในล็อบบี้ที่ดูเย็นชา (และไม่น่าสนใจ) ห้องพักกว้างขวางมาก มีระเบียงมองเห็นสระว่ายน้ำและวิวแม่น้ำในระยะไกล สะดวกสบาย ห้องน้ำขนาดใหญ่และมีอุปกรณ์ครบครันพร้อมเครื่องใช้ในห้องน้ำฟรี อาหารเช้ามีให้เลือกมากมาย หลากหลาย และคุณภาพดี อย่างไรก็ตาม โรงแรมมีราคาค่อนข้างสูงในเดือนมกราคม</t>
+          <t>ห้องพักสะอาดเงียบดีนอนหลับสะบายคะ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>K WUDDY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ทำเลดี   เดินทางสะดวก​  ไกล้แหล่งท่องเที่ยว​ ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>hello ! Bangkok _thailand2020 channel</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>บริการดีค่ะ.. ห้องพักสะอาด ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Somkieat</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ดี ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>พิชชาภา ศรียัง</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ เหมาะสำหรับเด็ก คุ้มค่า และ ไฮเทค</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ณรงค์ เนื้อไม้</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>piyawan khantha</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>สะอาด ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>nutsirin Jettavong</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>เดินทางสะดวก ปลอดภัย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Passenger62595953708</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมแห่งนี้ตั้งอยู่ในทำเลที่ดีมากบนถนนสุราวัง มีห้องพักที่กว้างขวาง สะอาด พร้อมน้ำดื่มวันละสองขวดและกาต้มน้ำสำหรับชงกาแฟหรือชา แม้ว่าห้องพักจะดูเก่าไปบ้าง แต่ก็คุ้มค่ากับราคา ห้องน้ำมีขนาดกำลังดีและใช้งานได้ดี อาหารเช้าแบบอะลาคาร์ตนั้นยอดเยี่ยม พนักงานเอาใจใส่และทำงานได้อย่างมีประสิทธิภาพ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ปรีญานุช อุสาหะ</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ลิฟต์เสียตลอดเวลา มาใช้งานเสียความรู้สึก ประเภทการเดินทาง ธุรกิจ ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1 ความปลอดภัย ไม่ดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>ประเสริฐ ห้วยหงษ์ทอง</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>โครตจะเริส ที่พักดีมากๆ พนักงานก็น่ารัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Saran Bunmalerd</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>นอนพักได้ หากไม่มีแขกข้างห้องจะสบายหู ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Oat Thanakiad</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>พื้นที่ตั้งของโรงแรมค่อนข้างจำกัดและติดกับตลาด ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 2 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Suppasek Ounsamai</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ลองดูเดี๋ยวรู้เลย ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Chariya Thiphathai</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมในห้าง สะดวก สบาย ใกล้แหล่งช้อปปิ้ง ราคาไม่แพง กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Phiranrat rujivorapat</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาดเดินทางสะดวกมีที่จอดรถ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 กิจกรรมในบริเวณใกล้เคียง อยู่ใกล้ห้างสรรพสินค้าเดอะมอลล์บางกะปิ ไฮไลต์ของโรงแรม วิวสวย และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>นิยุตเดช แย้มประนิตย์</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ดีสะดวก สะอาด อยู่ ถนนสีลม  พัฒน์พงษ์ ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>San Tong</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>ทำเลดี ห้องน่าจะปรับปรุงใหม่ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ปรับปรุงใหม่ ไม่มีกลิ่นอัพ กิจกรรมในบริเวณใกล้เคียง ชั้นล่าง เป็นห้าง แต่ปิดไวไปหน่อน ความปลอดภัย มี รปภ 24 ชม ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TK katekaew</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>มาประชุมสัมนา อาหารโอเค บริการดี ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Pueng Umaru</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานล็อบบี้หน้าไม่รับแขก พูดไม่น่าฟังเลย กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 1 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Tick Buu</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานน่ารักสุภาพชอบค่ะ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 4 ความปลอดภัย ดูแลดีมาก ไฮไลต์ของโรงแรม หรูหรา</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Load Za</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ทำไมย่อมดีกว่าเก่า สวยหรู ห้องพัก: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>May Tarot</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักสะอาด ใกล้แหล่งชอปปิ้ง ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 3 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ยอดรัก เเก่นทน</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>รถสวยออกง่าย ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Chopetch Thongpha</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักโอเค ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>thonwall kemthong</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>ใส่ใจดีมากครับ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Art CHUMINTARAJAK</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>หอพักสะอาดกว้างขวาง บรรยากาศดีวิวติดแม่น้ำกก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Chanont PICHAISIRI</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด อาหารอร่อย ลูกค้าชอบมากครับ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Sayumporn Srikamin</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด​ ห้องกว้างราคาไม่แพง​  พนักงานบริการดีมากๆๆๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา วิวสวย และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>บงกช สงวนพวก</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด กว้างขวาง สะดวกสบาย พนักงานเต็มใจบริการมากค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ห้องพัก กว้าง สะอาด สงบ ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Papholpat Phanuthanawat</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ห้องกว้างสะอาด ติดโบราณหน่อย อาหารปริมาณและรสชาติกลางๆ ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>YaiMai 17</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด​ อาหารอร่อย​ สระว่ายน้ำกว้าง❤️ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>มานิธ ธนคุณากาญจน์</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด​ ในตัวเมืองเดินทางสะดวกบริการดีมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>RUTCHAPONG SAN</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักกว้างสะอาด น่าพัก ครั้งหน้าจะมาพักที่นี่อีกแน่นอน ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>ผู้ใหญ่เดี่ยว</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ขอให้ตามใจผมเลยชอบเพลงเมือง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Noppadol Mutthaphal</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสวยมากวิวดีมาก ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ห้องพักสาวมากๆ ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Thidarat Khemphet</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักและบริการยอดเยี่ยม ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>กรภพ ธัญญกรณ์ภูวดล (กร ศรนารายณ์)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>อาหารสุดยอด ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Amorn</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอับอากาศไม่ถ่ายเท   น้ำอุ่นไม่ดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>ศุภชัย บุญเซ็ก</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>ห้องไม่สะอาดเท่าที่ควร.ไม่เหมาะกับการพักผ่อน ห้องพัก: 2 บริการ: 4 สถานที่ตั้ง: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Chayutra Chairuanka</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>เป็นสถานที่ที่เหมาะสำหรับออกกำลังกาย การบริการดีค่ะ ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>kitisak intasian</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ถนนภายในรีสอร์ทยังไม่ได้ลาดยางเลย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Wittawadee Sriyapan</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>เงียบสงบ สระว่ายน้ำใหญ่มาก พักสบาย สไตล์รีสอร์ท ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>ธราธิป ลักษณะวิจิตร</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ดีทุกอย่าง ยกเว้นเรื่องถนนทางเข้าควรปรับปรุงให้ดีด้วยครับ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาดดีมาก ความปลอดภัย มีเจ้าหน้าที่ตำรวจมาตรวจรู้สึกปลอดภัย อาหารและเครื่องดื่ม อร่อยดูดีมีระดับ ไฮไลต์ของโรงแรม วิวสวย และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>นิคม บุญโญรส</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>มีสระว่ายน้ำมาตรฐ่าน 16+50 เมตร ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Wadchanee 10</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ประทับใจในห้องในและการบริการ เเละ เงียบสงบเป็นส่วนตัว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>อนันต์ มาลัย</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>บริเวณโรงแรมกว้างขวาง ร่มรื่น  สระว่ายน้ำใหญ่มาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Mackie Tammy</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>เก่าไปหน่อยแต่คุ้มค่ากับราคาและมีสระว่ายน้ำให้เล่น ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>M Rpsert</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>มที่สามารถ ร่มรื่น ต้นไม้เยอะ อาหารอร่อย สงบ ประเภทการเดินทาง ธุรกิจ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Hdhjd Gdhjf</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>สะอาดบรรยากาศโรแมนติกมากๆครับ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Sutilux Tawabut</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>น้ำแรง โฟมแรง ลมเป่าแรง ราคาถูก ทำเลดีครับ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>สมพิศ บุญโชติ</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ดีมาก ห้องพัก: 5 บริการ: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>รถแดงเชียงใหม่ สองแถวเที่ยวเชียงใหม่</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ธรรมชาติมากดสำหรับในตัวเมืองเชียงใหม่ครับ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Lek Phanvijitsiri</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>บริการดี อาหารเช้าดีครบทุกอย่าง ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PU NA PHA CHOM ปู นา พา ชม</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ราคาไม่แพง แอร์เย็น นอนสบาย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Hansa Namhom</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศธรรมชาติดี พนักงานให้บริการดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>SPV Cafe</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>บรรกาศดี ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Saran Chaiyakut</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>5ดาว โดยแท้ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>phimphisa Kittimahacharoen</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศสงบ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>กัญญาวรรณ วิวัฒน์ทรงชัย</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด สดวกในการเดินทาง ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>เกษสุดา ยิ้มประสาททอง</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>โดยรวมก็โอเครนะค่ะ ด้านหลังที่พักมีตลาดค่ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 4 ห้องพัก ที่พักพอใช้ได้ สะอาด ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Kaland Adame</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>สะดวกสบาย อาหารอร่อย ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>ศศิชา กรานมูล</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ทุกอย่างดี  ห้องพีกสะอาด แาหารอร่อย ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>วศ.วรัท มาดีประเสริฐ</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>หลังโรงแรม คือ ตลาดไนท์บาร์ซ่าร์ ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>กมลภพ กรานมูล</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด มีอาหารนานาชาติ. ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>PRS Wako</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>สะดวกครับ ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>สิทธิชัย มูสิกรังศรี</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>เงียบสงบคับบรรยากาศดี ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Trip.com Member</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมสะอาดมากและบริการก็เป็นที่น่าพอใจ สิ่งอำนวยความสะดวกอยู่ในระดับปานกลาง แต่เมื่อเทียบกับราคาแล้วถือว่าคุ้มค่ามาก ตลาดกลางคืนอยู่ติดกับโรงแรม ซึ่งสะดวกมาก คุณสามารถหาอาหารและเครื่องดื่มได้ในระยะเดินไม่ไกล</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>THATPHONG THEPCHA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>โดยรวมแล้ว ดีเลย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ดี สะอาด เรียบร้อย ความสามารถเดินได้ ทั่วไป ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Somchai Sansomboonsuk</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมอยู่ตำแหน่งที่ดี มีลานจอดรถพอสมควร ห้องพักสะอาด ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 3 บริการ: 1 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Wilaiwan Sriwandee</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ดีมากค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม โรแมนติก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nueng Ct.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>ใกล้ถนนคนเดิน, เตียงดี หมอนสูงไป, ห้องน้ำกว้าง, มีที่จอดรถ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Supanna Khamrak</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>บริการดี ห้องพักสะอาดค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>วนิรา พุ่มฉัตร</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>ที่จอดรถสะดวกตรงข้ามประตูท่าแพมีร้านฟาสฟู๊ดอยู่กน้าโรงแรม ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Art Wang</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ดีมากๆ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Nichapatree Kanchana (TREE)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>ที่จอดรถอยู่ด้านหลัง  ทางเข้าเดียวกับแมคโดนัล ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>WITAYA - BANK - 陈银行 TANGKITPHATIKUL</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ห้องสวยมากครับ ทำเลดี ตรงข้ามประตูท่าแพ ใจกลางเมืองเลยครับ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Aced 4V</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักดีแต่ที่จอดรถน้อยมาก ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Krydtin Rojwarawat</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>พื้นห้องมีฝุ่นเยอะมาก ห้องน้ำมีกลิ่นนิดๆ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 3 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Malee Panlam Lekzaa</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>เตียงนุ่มนอนสบาย แอร์เย็นฉ่ำ อาหารเช้าอร่อย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Surud Soudon</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>วิวดีต้องห้อง 331 มีที่จอดรถด้านหลังสะดวกสะบาย ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>WhaWha TheinThein</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมเชียงใหม่ ประตูท่าแพ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>tachasit tunsakul</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักสะอาดอยู่ติดประตูท่าแพ ชั้นแรกมีMax ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>ธนกร ธีระสุคนธ์</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ปลั๊กไฟน่าจะมีเพิ่มให้อีกตรงข้างที่นอน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>จรรยารักษ์ พรมรินทร์</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักอยู่ใกล้ประตูท่าแพและอยู่ใกล้แหล่งอาหาร ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Meji Mettawong</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ดีมากค่ะะ สระว่ายน้ำใหญ่สนุกมากกก✌🏻🤟🏻 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>สุดใจ คําเลิศ</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด พนักงานบริการดีมาก สระว่ายน้ำสวย ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>tidnara จันสลี</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมสวยครับ มีสมาร์ททีวีด้วย ประเภทการเดินทาง วันหยุดพักผ่อน</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Suradech T.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ห้องสะอาด บรรยากาศดี เหมาะสำหรับการพักมากครับ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Tanaporn Hontong</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>อาหารเช้าหลากหลาย สระว่ายน้ำใหญ่ พนักงานบริการดีมาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Livingmuseum pichetchantarathiparak</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>อากาศดี บรรยากาศดี เค้กและเครื่องดื่มอร่อย บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>ธิดารัตน์</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด พนักงานบริการดีมาก สระว่ายน้ำใหญ่มาก แนะนำค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>IWARIN i</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>สะอาด ราคาดี อาหารอร่อย อาหารเข้าเยอะ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Kamalaporn Pringuthumporn</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ห้องดีนอนสบาย อาหารเช้าดี ที่จอดรถดี คุ้มค่ามาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Waraporn Uppamaye</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานบริการดี บรรยากาศโรงแรมสวยงาม ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Khodchakorn Onsrithong</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ที่นอนนุ่มมาก นอนสบาย ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>ลุงตุ๊ ครับผม</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>จองจากกรุงเทพมา ก็สะดวกพอสมควร ประเภทการเดินทาง วันหยุดพักผ่อน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>อมรกาญจน์ แจ่มสว่าง</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>สถานที่สะอาด บรรยากาศร่มรื่น บริการดี อาหารสะอาด รสชาติดี ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Kitipong Klamkongkool</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศรอบๆ เป็นที่พักยุค 90 ไกลจุดตลาดและของกินไปหน่อย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>นงเยาว์ เผ่าเผือก</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>จัดงานเลี้ยงใหญ่ๆได้สบายมาก สถานที่กว้างขวาง อาหารก็okค่ะ บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Roong SigP229</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>สถานที่กว้างขวางมาก ภูมิทรรศงดงามห้องพักดี อาหารเช้าเยี่ยม ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Aqpitsara Noiburie</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานดูแลดีมาก โดยเฉพาะในส่วนห้องอาหารน้องๆน่ารักมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Krittiya Sodram</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด อาหารอร่อยมากค่ะ พนักงานดูแลดีค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Sittichai Suwonprateep</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>สะอาด กว้างขวาง บริการดี อาหารเช้าเยอะมากๆๆๆๆ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nong Sutthawan</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ห้องกว้างขวาง แต่มีจุดเสียบปลั๊กไฟน้อย ไม่สะดวกต่อการใช้งาน ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Pen ek</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Trainer บี บริการดีมากเป็นกันเองสุดๆ เข้าถึงง่าย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Saowanee Jinakul</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานเป็นกันเอง ยิ้มแย้ม บรรยากาศดี อาหารอร่อย ห้องพักดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ห้องพักสวย ที่นอนใหม่ นุ่มสบาย กิจกรรมในบริเวณใกล้เคียง ใกล้ตลาดนัดเดินไม่ไกล ความปลอดภัย มีกล้องวงจรปิด ตามจุดสาธารณะ ความสามารถเดินได้ สะดวกสบาย เดินทางง่าย อาหารและเครื่องดื่ม อาหารอร่อย บุฟเฟ่มีให้เลือกหลากหลาย รายละเอียดที่น่าสนใจ ที่จอดรถกว้างขวาง ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>RG CY</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักสะอาด อาหารอร่อย พนักงานบริการดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Almond Iyarin</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ขอบคุณคุณยะ ที่ให้คำแนะนำดี ใส่ใจลูกค้าอยู่ตลอดค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>AOi Aoi</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักดีสะอาดพักเป็นครั้งที่สองแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>ประคอง ทองใหญ่</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานบริการดีเยี่ยม ห้องพักสะอาด อาหารเช้าหลากหลาย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ห้องพักสะอาด กิจกรรมในบริเวณใกล้เคียง สะดวกใกล้ตลาดไนท์บ้านเกาะ ความปลอดภัย มีระบบรักษาความปลอดภัยดีเยี่ยม ความสามารถเดินได้ สะดวกต่อการเดินทาง อยู่ในตัวเอง อาหารและเครื่องดื่ม อาหารเช้ามีให้เลือกหลากหลาย รายละเอียดที่น่าสนใจ ใกล้ห้างเซ็นทรัล ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Butdee Korlee</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>อาหารอร่อย ห้องพักดีสะอาด ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาดดี กิจกรรมในบริเวณใกล้เคียง ดีมาก ความปลอดภัย มีรปภ. ความสามารถเดินได้ ใกล้แหล่งอาหาร อาหารและเครื่องดื่ม ดีมาก เช้า กลาง บุฟเฟต์ รายละเอียดที่น่าสนใจ ใกล้ที่สถานที่ท่องเที่ยว ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>P. T.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>ที่นอนยวบเกิน นอนละปวดหลัง ประเภทการเดินทาง ธุรกิจ ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>สวนพิณ ศรีราชา</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>น้ำเบามาก กับข้าวพื้นๆ ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>ฑิญาดา ดีด่านค้อ</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ขนมเบรคอร่อย ใกล้ตลาดไนท์ พนักงานน่ารัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Thanyathon _Mintny</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>ขนมเบรคอร่อยมาใกล้เซนทรัลและตลาดไนท์เกาะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Wee Weevy</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>แม่บ้านน่ารักพูดจาสุภาพดี👍👍👍 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>นิญาวดี เพ็ชรทะเล</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>อาหารอร่อยบริการดีมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BUNEEEYA BINGDOLOH</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมนรา มีสระว่ายน้ำ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>วิชญา หาญนัทธี</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักเก่าไปหน่อย แต่สะอาดและได้รับการปรับปรุงบ้างแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Ananda Phikunthong</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ห้องกว้างมากค่ะ สมราคาค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Kampol srirat</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>สภานที่ตั้งไกล้ตลาดเช้าเหมาะสำหรับเลือกซื้อของกินของฝาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Chanchai Muangmoon</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักในเมืองนราธิวาส สะอาด มีสระว่ายน้ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 4 กิจกรรมในบริเวณใกล้เคียง มีตลาดสดหน้า รร เดินทางปลอดภัยและสะดวก ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Natapong Warnearng</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>ห้องมีซากแมลงสาปตายห้องน้ำเหลืองอ๋อย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>kedsarin Pinyojit</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>พรุ่งนี้จะเข้าพัก พึ่งมาอ่านรีวิว กลัวผิดหวังจัง ประเภทการเดินทาง ธุรกิจ บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Kanjanawan Nilklud</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>ห้องกว้าง สะอาด มีไดร์เป่าผม ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Phatthanan</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมใหญ่ มีที่จอดรถ ห้องพัก: 4 บริการ: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Chutibhond Jaiwong</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ห้องใหญ่ บรรยากาศดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>วสุ ขัติยสุรินทร์</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>สถานที่ตั้งอยู่กลางเมืองง่ายต่อการเดืนทาง ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ความสามารถเดินได้ อยู่หน้าตลาดร้านค้ามากมาย ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Jakita WisaisoponKul</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>เป็นโรงแรมเก่าแก่ราคาค่อนข้างสูง ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Noppadol Mutthaphal</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>ราคาและบริการเหมาะสมกับการเดินทางเพื่อดำเนินธุรกิจ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ความปลอดภัย มีความปลอดภัยสูง ความสามารถเดินได้ เดินทางได้สะดวก ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>บุญศักดิ์ แซ่ซิม</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>อากาศดี.ไม่พลุกพาน. ไฮไลต์ของโรงแรม โรแมนติก</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>นาซนีน นานา</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>บริการดีชอบคุยกันเองยิ้มแย้ม ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>มานะ แซ่เฮง</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>อยู่ในเมืองเงียบสงบไม่วุ่นวาย ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Madukan Chanel.</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดี อาหารอร่อยมาก ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Cheaesoh Cheyor</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>อาหารอร่อยมากๆ ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>ผจญ สุริยะวงศ์</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>สอาด โอ่โถง บริการดี ใกล้ตลาด ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 4 สถานที่ตั้ง: 5 ห้องพัก น่าพักมาก สอาด ไม่แพง ที่จอดรถสะดวก ความปลอดภัย ความปลอดภัยสูง ไฮไลต์ของโรงแรม โรแมนติก และ เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Pannida Uadhaw</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>ต้นไม้เยอะ ยุงเลยชุม ตอนกลางคืนได้ยินเสียงหนูแทะไม้ทั้งคืน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>ทรงพล เมฆพัฒน์</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>เงียบสงบมากครับ อ่างอาบน้ำมีรูใช้ไม่ได้ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>์NUCHIT WERASING</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักที่ดี อีกที่ในเชียงใหม่ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>กาญจน์ เมืองที่รัก</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>ห้องดี สะอาด บริการสุภาพ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>ช.ตุ้ย ครับบบ อินแปดริ้ว</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักใหญ่มาก ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>shuu suk</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>เคยไปใช้บริการสระว่ายน้ำ​ โอเคเลยครับ บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Supak Som</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>ประทับใจมากๆ ที่พักดี อาหารอร่อย พนักงานดูแลดีมากๆๆ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>ประเสริฐศักดิ์ ชื่นจิตร</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศร่มรื่นดีมาก ๆ แต่ห้อง 4113 แอร์ไม่เย็น ห้องพัก: 4 บริการ: 2 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Black N</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>ห้องสะอาด ผ้าห่มที่นอนสะอาดมาก ราคาเบา ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Narin Chutiphattharasakul</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>ต้องมาอีก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย โรแมนติก เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>sinchai puwadet Prachayapaisal</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ดีครับสวยงามมากๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Nongluk Lokakalin</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>สนุกมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>simone Xie</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>สวยจัง กลุ่มท่องเที่ยว เดินทางลำพัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>kritsada posprasit</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดีใจกลางเมือง ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -1849,7 +5339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2180,6 +5670,226 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>RWC</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>TSB</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
